--- a/artfynd/A 55253-2022 artfynd.xlsx
+++ b/artfynd/A 55253-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111224895</v>
+        <v>105310606</v>
       </c>
       <c r="B2" t="n">
-        <v>57124</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100100</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Görsviken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591595</v>
+        <v>591540</v>
       </c>
       <c r="R2" t="n">
-        <v>6831280</v>
+        <v>6831453</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten, troligen varning då den flög upp när vi kom gående</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,23 +757,755 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lövrik och örtrik barrnaturskog</t>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>105315101</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92208</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>658</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Görsviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>591554</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6831449</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nianfors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>105315100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Görsviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>591558</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6831453</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nianfors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>105315102</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Görsviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>591554</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6831450</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nianfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>105315103</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Görsviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>591543</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6831441</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nianfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>105311819</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Görsviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>591543</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6831444</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nianfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111224895</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57838</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100100</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bivråk</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pernis apivorus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Görsviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>591595</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6831280</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nianfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten, troligen varning då den flög upp när vi kom gående</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Lövrik och örtrik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Sebastian Kirppu, Karolin Hård</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111224894</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Görsviken, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>591510</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6831427</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nianfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lövrik och örtrik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>mossig mark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, Karolin Hård</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
